--- a/ch_04_eda/ch_04_solution.xlsx
+++ b/ch_04_eda/ch_04_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_04_eda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_04_eda\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B004FD-9DF2-462B-893C-D6490057C83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1977,19 +1977,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K399"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.1171875" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.41015625" customWidth="1"/>
-    <col min="5" max="5" width="8.1171875" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="5" max="5" width="8.1328125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.234375" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>18</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>15</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>16</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>17</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>15</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>15</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>15</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>14</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>15</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>24</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>22</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>18</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>21</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>27</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>26</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>25</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>24</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>25</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>26</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>21</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>11</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>9</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>25</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>25</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>19</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>16</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>17</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>19</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>18</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>14</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>14</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>14</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>14</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>12</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>13</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>13</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>18</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>22</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>19</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>18</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>23</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>28</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>30</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>30</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>31</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>35</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>27</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>26</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>24</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>25</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>23</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>20</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>21</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>13</v>
       </c>
@@ -3846,7 +3846,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>14</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>15</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>14</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>17</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>11</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>13</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>12</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>13</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>19</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>15</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>13</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>13</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>14</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>18</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>22</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>21</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>26</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>22</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>28</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>23</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>28</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>27</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>13</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>14</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>13</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>14</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>15</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>12</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>13</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>13</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>14</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>13</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>13</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>18</v>
       </c>
@@ -4861,7 +4861,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>16</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>18</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>18</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>23</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>26</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>11</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>12</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>13</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>12</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>18</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>20</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>21</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>22</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>18</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>19</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>21</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>26</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>15</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>16</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>29</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>24</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>20</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>19</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>15</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>24</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>20</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>11</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>20</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>21</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>19</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>15</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>31</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>26</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>32</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>25</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>16</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>16</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>18</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>16</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>13</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>14</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>14</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>14</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>29</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>26</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>26</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>31</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>32</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>28</v>
       </c>
@@ -6279,7 +6279,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>24</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>26</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>24</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>26</v>
       </c>
@@ -6395,7 +6395,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>31</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>19</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>18</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>15</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>15</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>16</v>
       </c>
@@ -6569,7 +6569,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>15</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>16</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>14</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>17</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>16</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>15</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>18</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>21</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>20</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>13</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>29</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>23</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>20</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>23</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>24</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>25</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>24</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>18</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>29</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>19</v>
       </c>
@@ -7149,7 +7149,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>23</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>23</v>
       </c>
@@ -7207,7 +7207,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>22</v>
       </c>
@@ -7236,7 +7236,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>25</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>33</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>28</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>25</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>25</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>26</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>27</v>
       </c>
@@ -7439,7 +7439,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>17.5</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>16</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>15.5</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>14.5</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>22</v>
       </c>
@@ -7584,7 +7584,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>22</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>24</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>22.5</v>
       </c>
@@ -7671,7 +7671,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>29</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>24.5</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>29</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>33</v>
       </c>
@@ -7787,7 +7787,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>20</v>
       </c>
@@ -7816,7 +7816,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>18</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>18.5</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>17.5</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>29.5</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>32</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>28</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>26.5</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>20</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>13</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>19</v>
       </c>
@@ -8106,7 +8106,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>19</v>
       </c>
@@ -8135,7 +8135,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>16.5</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>16.5</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>13</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>13</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>13</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>31.5</v>
       </c>
@@ -8309,7 +8309,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>30</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>36</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>25.5</v>
       </c>
@@ -8396,7 +8396,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>33.5</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>17.5</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>17</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>15.5</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>15</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>17.5</v>
       </c>
@@ -8570,7 +8570,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>20.5</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>19</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>18.5</v>
       </c>
@@ -8657,7 +8657,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>16</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>15.5</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>15.5</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>16</v>
       </c>
@@ -8773,7 +8773,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>29</v>
       </c>
@@ -8802,7 +8802,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>24.5</v>
       </c>
@@ -8831,7 +8831,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>26</v>
       </c>
@@ -8860,7 +8860,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>25.5</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>30.5</v>
       </c>
@@ -8918,7 +8918,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>33.5</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>30</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>30.5</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>22</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>21.5</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>21.5</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>43.1</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>36.1</v>
       </c>
@@ -9150,7 +9150,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>32.799999999999997</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>39.4</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>36.1</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>19.899999999999999</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>19.399999999999999</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>20.2</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>19.2</v>
       </c>
@@ -9353,7 +9353,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>20.5</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>20.2</v>
       </c>
@@ -9411,7 +9411,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>25.1</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>20.5</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>19.399999999999999</v>
       </c>
@@ -9498,7 +9498,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>20.6</v>
       </c>
@@ -9527,7 +9527,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>20.8</v>
       </c>
@@ -9556,7 +9556,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>18.600000000000001</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>18.100000000000001</v>
       </c>
@@ -9614,7 +9614,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>19.2</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>17.7</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>18.100000000000001</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>17.5</v>
       </c>
@@ -9730,7 +9730,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>30</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>27.5</v>
       </c>
@@ -9788,7 +9788,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>27.2</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>30.9</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>21.1</v>
       </c>
@@ -9875,7 +9875,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>23.2</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>23.8</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>23.9</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>20.3</v>
       </c>
@@ -9991,7 +9991,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>17</v>
       </c>
@@ -10020,7 +10020,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>21.6</v>
       </c>
@@ -10049,7 +10049,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>16.2</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>31.5</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>29.5</v>
       </c>
@@ -10136,7 +10136,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>21.5</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>19.8</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>22.3</v>
       </c>
@@ -10223,7 +10223,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>20.2</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>20.6</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10310,7 +10310,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>17.600000000000001</v>
       </c>
@@ -10339,7 +10339,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>16.5</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>18.2</v>
       </c>
@@ -10397,7 +10397,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>16.899999999999999</v>
       </c>
@@ -10426,7 +10426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>15.5</v>
       </c>
@@ -10455,7 +10455,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>19.2</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>18.5</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>31.9</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>34.1</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>35.700000000000003</v>
       </c>
@@ -10600,7 +10600,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>27.4</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>25.4</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>23</v>
       </c>
@@ -10687,7 +10687,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>27.2</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>23.9</v>
       </c>
@@ -10745,7 +10745,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>34.200000000000003</v>
       </c>
@@ -10774,7 +10774,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>34.5</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>31.8</v>
       </c>
@@ -10832,7 +10832,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>37.299999999999997</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>28.4</v>
       </c>
@@ -10890,7 +10890,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>28.8</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>26.8</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>33.5</v>
       </c>
@@ -10977,7 +10977,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>41.5</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>38.1</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>32.1</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>37.200000000000003</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>28</v>
       </c>
@@ -11122,7 +11122,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>26.4</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>24.3</v>
       </c>
@@ -11180,7 +11180,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>19.100000000000001</v>
       </c>
@@ -11209,7 +11209,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>34.299999999999997</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>29.8</v>
       </c>
@@ -11267,7 +11267,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>31.3</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>37</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>32.200000000000003</v>
       </c>
@@ -11354,7 +11354,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>46.6</v>
       </c>
@@ -11383,7 +11383,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>27.9</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>40.799999999999997</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>44.3</v>
       </c>
@@ -11470,7 +11470,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>43.4</v>
       </c>
@@ -11499,7 +11499,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>36.4</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>30</v>
       </c>
@@ -11557,7 +11557,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>44.6</v>
       </c>
@@ -11586,7 +11586,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>40.9</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>33.799999999999997</v>
       </c>
@@ -11641,7 +11641,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>29.8</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>32.700000000000003</v>
       </c>
@@ -11699,7 +11699,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>23.7</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>35</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>23.6</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>32.4</v>
       </c>
@@ -11812,7 +11812,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>27.2</v>
       </c>
@@ -11841,7 +11841,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>26.6</v>
       </c>
@@ -11870,7 +11870,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>25.8</v>
       </c>
@@ -11899,7 +11899,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>23.5</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>30</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>39.1</v>
       </c>
@@ -11986,7 +11986,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>39</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>35.1</v>
       </c>
@@ -12044,7 +12044,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>32.299999999999997</v>
       </c>
@@ -12073,7 +12073,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>37</v>
       </c>
@@ -12102,7 +12102,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>37.700000000000003</v>
       </c>
@@ -12131,7 +12131,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>34.1</v>
       </c>
@@ -12160,7 +12160,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>34.700000000000003</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>34.4</v>
       </c>
@@ -12218,7 +12218,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>29.9</v>
       </c>
@@ -12247,7 +12247,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>33</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>34.5</v>
       </c>
@@ -12302,7 +12302,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>33.700000000000003</v>
       </c>
@@ -12331,7 +12331,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>32.4</v>
       </c>
@@ -12360,7 +12360,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>32.9</v>
       </c>
@@ -12389,7 +12389,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>31.6</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>28.1</v>
       </c>
@@ -12447,7 +12447,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>30.7</v>
       </c>
@@ -12476,7 +12476,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>25.4</v>
       </c>
@@ -12505,7 +12505,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>24.2</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>22.4</v>
       </c>
@@ -12563,7 +12563,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>26.6</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>20.2</v>
       </c>
@@ -12621,7 +12621,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>17.600000000000001</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>28</v>
       </c>
@@ -12679,7 +12679,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>27</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>34</v>
       </c>
@@ -12737,7 +12737,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>31</v>
       </c>
@@ -12766,7 +12766,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>29</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>27</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>24</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>23</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>36</v>
       </c>
@@ -12908,7 +12908,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>37</v>
       </c>
@@ -12937,7 +12937,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>31</v>
       </c>
@@ -12966,7 +12966,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>38</v>
       </c>
@@ -12995,7 +12995,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>36</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>36</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>36</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>34</v>
       </c>
@@ -13111,7 +13111,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>38</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>32</v>
       </c>
@@ -13169,7 +13169,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>38</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>25</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>38</v>
       </c>
@@ -13256,7 +13256,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>26</v>
       </c>
@@ -13285,7 +13285,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>22</v>
       </c>
@@ -13314,7 +13314,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>32</v>
       </c>
@@ -13343,7 +13343,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>36</v>
       </c>
@@ -13372,7 +13372,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>27</v>
       </c>
@@ -13401,7 +13401,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>27</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>44</v>
       </c>
@@ -13459,7 +13459,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>32</v>
       </c>
@@ -13488,7 +13488,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>28</v>
       </c>
@@ -13517,7 +13517,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>31</v>
       </c>
@@ -13558,19 +13558,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FBD565-4521-4E30-A67D-FF1FDA2E9337}">
   <dimension ref="A1:I95"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.234375" customWidth="1"/>
-    <col min="2" max="2" width="30.3515625" customWidth="1"/>
-    <col min="3" max="3" width="11.76171875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.17578125" customWidth="1"/>
-    <col min="6" max="6" width="10.46875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1171875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.05859375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.19921875" customWidth="1"/>
+    <col min="6" max="6" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="str" cm="1">
         <f t="array" ref="A1:F10">_xlfn._xlws.PY(1,0)</f>
         <v/>
@@ -13591,7 +13591,7 @@
         <v>unique</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
         <v>mpg</v>
       </c>
@@ -13611,7 +13611,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
         <v>cylinders</v>
       </c>
@@ -13631,7 +13631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
         <v>displacement</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
         <v>horsepower</v>
       </c>
@@ -13671,7 +13671,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
         <v>weight</v>
       </c>
@@ -13691,7 +13691,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
         <v>acceleration</v>
       </c>
@@ -13711,7 +13711,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
         <v>model_year</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="str">
         <v>origin</v>
       </c>
@@ -13751,7 +13751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <v>name</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="str" cm="1">
         <f t="array" ref="A14:I19">_xlfn._xlws.PY(2,0)</f>
         <v>mpg</v>
@@ -13801,7 +13801,7 @@
         <v>name</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>18</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>chevrolet chevelle malibu</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>buick skylark 320</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>18</v>
       </c>
@@ -13888,7 +13888,7 @@
         <v>plymouth satellite</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -13917,7 +13917,7 @@
         <v>amc rebel sst</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -13946,19 +13946,19 @@
         <v>ford torino</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="str" cm="1">
         <f t="array" ref="A21">_xlfn._xlws.PY(3,0)</f>
         <v>Before: 398 rows, After: 392 rows, Removed: 6</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="str" cm="1">
         <f t="array" ref="A23">_xlfn._xlws.PY(4,0)</f>
         <v>Median horsepower: 93.5, Missing after fill: 0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="str" cm="1">
         <f t="array" ref="A25:C30">_xlfn._xlws.PY(5,0)</f>
         <v>name</v>
@@ -13970,7 +13970,7 @@
         <v>era</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="str">
         <v>chevrolet chevelle malibu</v>
       </c>
@@ -13981,7 +13981,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="str">
         <v>buick skylark 320</v>
       </c>
@@ -13992,7 +13992,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="str">
         <v>plymouth satellite</v>
       </c>
@@ -14003,7 +14003,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="str">
         <v>amc rebel sst</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="str">
         <v>ford torino</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="str" cm="1">
         <f t="array" ref="A33:B36">_xlfn._xlws.PY(6,0)</f>
         <v>origin</v>
@@ -14034,7 +14034,7 @@
         <v>power_to_weight</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="str">
         <v>europe</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>33.69</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="str">
         <v>japan</v>
       </c>
@@ -14050,7 +14050,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="str">
         <v>usa</v>
       </c>
@@ -14058,7 +14058,7 @@
         <v>34.97</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="str" cm="1">
         <f t="array" ref="A39:F43">_xlfn._xlws.PY(7,0)</f>
         <v>cylinders</v>
@@ -14079,7 +14079,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="str">
         <v>origin</v>
       </c>
@@ -14099,7 +14099,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="str">
         <v>europe</v>
       </c>
@@ -14119,7 +14119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="str">
         <v>japan</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="str">
         <v>usa</v>
       </c>
@@ -14159,7 +14159,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" t="str" cm="1">
         <f t="array" ref="A46:F50">_xlfn._xlws.PY(8,0)</f>
         <v>cylinders</v>
@@ -14180,7 +14180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" t="str">
         <v>origin</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" t="str">
         <v>europe</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" t="str">
         <v>japan</v>
       </c>
@@ -14240,7 +14240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" t="str">
         <v>usa</v>
       </c>
@@ -14260,19 +14260,19 @@
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" t="e" cm="1" vm="2">
         <f t="array" ref="A54">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A74" t="e" cm="1" vm="3">
         <f t="array" ref="A74">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="str" cm="1">
         <f t="array" ref="A89:G92">_xlfn._xlws.PY(11,0)</f>
         <v/>
@@ -14296,7 +14296,7 @@
         <v>model_year</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>344</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>378</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>387</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="e" cm="1" vm="4">
         <f t="array" ref="A95">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>

--- a/ch_04_eda/ch_04_solution.xlsx
+++ b/ch_04_eda/ch_04_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_04_eda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B004FD-9DF2-462B-893C-D6490057C83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8603F6F-2B34-4614-9750-0CD8BBE86C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="14586" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -214,18 +214,26 @@
 outliers[["name", "mpg", "cylinders", "horsepower", "weight", "model_year"]] </code>
     </pythonScript>
     <pythonScript>
-      <code>mpg_df["outlier"] = (mpg_df["origin"] == "usa") &amp; (mpg_df["mpg"] &gt; upper_bound)
+      <code>usa = mpg_df.loc[mpg_df["origin"] == "usa"].copy()
+usa["is_outlier"] = np.where(
+    (usa["mpg"] &gt; upper_bound) | (usa["mpg"] &lt; lower_bound),
+    "Yes", "No"
+)
 plt.figure(figsize=(9, 6))
 sns.scatterplot(
-    x="weight", y="mpg", hue="outlier", data=mpg_df,
-    palette={False: "steelblue", True: "red"},
-    alpha=0.6, style="outlier",
-    markers={False: "o", True: "X"}, s=60
+    x="weight", y="mpg",
+    hue="is_outlier", style="is_outlier",
+    data=usa,
+    hue_order=["No", "Yes"],
+    style_order=["No", "Yes"],
+    palette={"No": "steelblue", "Yes": "red"},
+    markers={"No": "o", "Yes": "X"},
+    alpha=0.6, s=60
 )
-plt.title("Weight vs. MPG with High-MPG American Outliers Highlighted")
+plt.title("American Vehicles: Weight vs. MPG with Outliers Highlighted")
 plt.xlabel("Vehicle Weight (lbs)")
 plt.ylabel("Miles per Gallon")
-plt.legend(title="High-MPG Outlier", labels=["No", "Yes"])</code>
+plt.legend(title="MPG Outlier")</code>
     </pythonScript>
   </pythonScripts>
 </python>
@@ -1638,7 +1646,7 @@
     </spb>
     <spb s="2">
       <v>https://www.anaconda.com/excel</v>
-      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
+      <v>https://res.cdn.office.net/officepysvc/prod-service/anacondalogo.png</v>
       <v>Python provided by Anaconda</v>
     </spb>
   </spbData>
@@ -1977,19 +1985,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K399"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1171875" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" customWidth="1"/>
-    <col min="5" max="5" width="8.1328125" customWidth="1"/>
+    <col min="4" max="4" width="12.41015625" customWidth="1"/>
+    <col min="5" max="5" width="8.1171875" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" customWidth="1"/>
+    <col min="7" max="7" width="12.17578125" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2022,7 +2030,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A2">
         <v>18</v>
       </c>
@@ -2051,7 +2059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A3">
         <v>15</v>
       </c>
@@ -2080,7 +2088,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2109,7 +2117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A5">
         <v>16</v>
       </c>
@@ -2138,7 +2146,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A6">
         <v>17</v>
       </c>
@@ -2167,7 +2175,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A7">
         <v>15</v>
       </c>
@@ -2196,7 +2204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2225,7 +2233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2254,7 +2262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2283,7 +2291,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A11">
         <v>15</v>
       </c>
@@ -2312,7 +2320,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>15</v>
       </c>
@@ -2341,7 +2349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A13">
         <v>14</v>
       </c>
@@ -2370,7 +2378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A14">
         <v>15</v>
       </c>
@@ -2399,7 +2407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2428,7 +2436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A16">
         <v>24</v>
       </c>
@@ -2457,7 +2465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17">
         <v>22</v>
       </c>
@@ -2486,7 +2494,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18">
         <v>18</v>
       </c>
@@ -2515,7 +2523,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19">
         <v>21</v>
       </c>
@@ -2544,7 +2552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A20">
         <v>27</v>
       </c>
@@ -2573,7 +2581,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21">
         <v>26</v>
       </c>
@@ -2602,7 +2610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A22">
         <v>25</v>
       </c>
@@ -2631,7 +2639,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23">
         <v>24</v>
       </c>
@@ -2660,7 +2668,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A24">
         <v>25</v>
       </c>
@@ -2689,7 +2697,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A25">
         <v>26</v>
       </c>
@@ -2718,7 +2726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A26">
         <v>21</v>
       </c>
@@ -2747,7 +2755,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2776,7 +2784,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2805,7 +2813,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A29">
         <v>11</v>
       </c>
@@ -2834,7 +2842,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A30">
         <v>9</v>
       </c>
@@ -2863,7 +2871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2892,7 +2900,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2921,7 +2929,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33">
         <v>25</v>
       </c>
@@ -2950,7 +2958,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34">
         <v>25</v>
       </c>
@@ -2976,7 +2984,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35">
         <v>19</v>
       </c>
@@ -3005,7 +3013,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36">
         <v>16</v>
       </c>
@@ -3034,7 +3042,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37">
         <v>17</v>
       </c>
@@ -3063,7 +3071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38">
         <v>19</v>
       </c>
@@ -3092,7 +3100,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39">
         <v>18</v>
       </c>
@@ -3121,7 +3129,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40">
         <v>14</v>
       </c>
@@ -3150,7 +3158,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41">
         <v>14</v>
       </c>
@@ -3179,7 +3187,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42">
         <v>14</v>
       </c>
@@ -3208,7 +3216,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43">
         <v>14</v>
       </c>
@@ -3237,7 +3245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44">
         <v>12</v>
       </c>
@@ -3266,7 +3274,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45">
         <v>13</v>
       </c>
@@ -3295,7 +3303,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46">
         <v>13</v>
       </c>
@@ -3324,7 +3332,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47">
         <v>18</v>
       </c>
@@ -3353,7 +3361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48">
         <v>22</v>
       </c>
@@ -3382,7 +3390,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49">
         <v>19</v>
       </c>
@@ -3411,7 +3419,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50">
         <v>18</v>
       </c>
@@ -3440,7 +3448,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51">
         <v>23</v>
       </c>
@@ -3469,7 +3477,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52">
         <v>28</v>
       </c>
@@ -3498,7 +3506,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53">
         <v>30</v>
       </c>
@@ -3527,7 +3535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54">
         <v>30</v>
       </c>
@@ -3556,7 +3564,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55">
         <v>31</v>
       </c>
@@ -3585,7 +3593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56">
         <v>35</v>
       </c>
@@ -3614,7 +3622,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57">
         <v>27</v>
       </c>
@@ -3643,7 +3651,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58">
         <v>26</v>
       </c>
@@ -3672,7 +3680,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59">
         <v>24</v>
       </c>
@@ -3701,7 +3709,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60">
         <v>25</v>
       </c>
@@ -3730,7 +3738,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61">
         <v>23</v>
       </c>
@@ -3759,7 +3767,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62">
         <v>20</v>
       </c>
@@ -3788,7 +3796,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63">
         <v>21</v>
       </c>
@@ -3817,7 +3825,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64">
         <v>13</v>
       </c>
@@ -3846,7 +3854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65">
         <v>14</v>
       </c>
@@ -3875,7 +3883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66">
         <v>15</v>
       </c>
@@ -3904,7 +3912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67">
         <v>14</v>
       </c>
@@ -3933,7 +3941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68">
         <v>17</v>
       </c>
@@ -3962,7 +3970,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69">
         <v>11</v>
       </c>
@@ -3991,7 +3999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70">
         <v>13</v>
       </c>
@@ -4020,7 +4028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71">
         <v>12</v>
       </c>
@@ -4049,7 +4057,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72">
         <v>13</v>
       </c>
@@ -4078,7 +4086,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73">
         <v>19</v>
       </c>
@@ -4107,7 +4115,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74">
         <v>15</v>
       </c>
@@ -4136,7 +4144,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75">
         <v>13</v>
       </c>
@@ -4165,7 +4173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76">
         <v>13</v>
       </c>
@@ -4194,7 +4202,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77">
         <v>14</v>
       </c>
@@ -4223,7 +4231,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78">
         <v>18</v>
       </c>
@@ -4252,7 +4260,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79">
         <v>22</v>
       </c>
@@ -4281,7 +4289,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80">
         <v>21</v>
       </c>
@@ -4310,7 +4318,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81">
         <v>26</v>
       </c>
@@ -4339,7 +4347,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82">
         <v>22</v>
       </c>
@@ -4368,7 +4376,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83">
         <v>28</v>
       </c>
@@ -4397,7 +4405,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84">
         <v>23</v>
       </c>
@@ -4426,7 +4434,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85">
         <v>28</v>
       </c>
@@ -4455,7 +4463,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86">
         <v>27</v>
       </c>
@@ -4484,7 +4492,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87">
         <v>13</v>
       </c>
@@ -4513,7 +4521,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88">
         <v>14</v>
       </c>
@@ -4542,7 +4550,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89">
         <v>13</v>
       </c>
@@ -4571,7 +4579,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90">
         <v>14</v>
       </c>
@@ -4600,7 +4608,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91">
         <v>15</v>
       </c>
@@ -4629,7 +4637,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92">
         <v>12</v>
       </c>
@@ -4658,7 +4666,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93">
         <v>13</v>
       </c>
@@ -4687,7 +4695,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94">
         <v>13</v>
       </c>
@@ -4716,7 +4724,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95">
         <v>14</v>
       </c>
@@ -4745,7 +4753,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96">
         <v>13</v>
       </c>
@@ -4774,7 +4782,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4803,7 +4811,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98">
         <v>13</v>
       </c>
@@ -4832,7 +4840,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99">
         <v>18</v>
       </c>
@@ -4861,7 +4869,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100">
         <v>16</v>
       </c>
@@ -4890,7 +4898,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101">
         <v>18</v>
       </c>
@@ -4919,7 +4927,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102">
         <v>18</v>
       </c>
@@ -4948,7 +4956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103">
         <v>23</v>
       </c>
@@ -4977,7 +4985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104">
         <v>26</v>
       </c>
@@ -5006,7 +5014,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105">
         <v>11</v>
       </c>
@@ -5035,7 +5043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106">
         <v>12</v>
       </c>
@@ -5064,7 +5072,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107">
         <v>13</v>
       </c>
@@ -5093,7 +5101,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108">
         <v>12</v>
       </c>
@@ -5122,7 +5130,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109">
         <v>18</v>
       </c>
@@ -5151,7 +5159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110">
         <v>20</v>
       </c>
@@ -5180,7 +5188,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111">
         <v>21</v>
       </c>
@@ -5209,7 +5217,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112">
         <v>22</v>
       </c>
@@ -5238,7 +5246,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113">
         <v>18</v>
       </c>
@@ -5267,7 +5275,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114">
         <v>19</v>
       </c>
@@ -5296,7 +5304,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115">
         <v>21</v>
       </c>
@@ -5325,7 +5333,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116">
         <v>26</v>
       </c>
@@ -5354,7 +5362,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117">
         <v>15</v>
       </c>
@@ -5383,7 +5391,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118">
         <v>16</v>
       </c>
@@ -5412,7 +5420,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119">
         <v>29</v>
       </c>
@@ -5441,7 +5449,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120">
         <v>24</v>
       </c>
@@ -5470,7 +5478,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121">
         <v>20</v>
       </c>
@@ -5499,7 +5507,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A122">
         <v>19</v>
       </c>
@@ -5528,7 +5536,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A123">
         <v>15</v>
       </c>
@@ -5557,7 +5565,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A124">
         <v>24</v>
       </c>
@@ -5586,7 +5594,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A125">
         <v>20</v>
       </c>
@@ -5615,7 +5623,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A126">
         <v>11</v>
       </c>
@@ -5644,7 +5652,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A127">
         <v>20</v>
       </c>
@@ -5673,7 +5681,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A128">
         <v>21</v>
       </c>
@@ -5699,7 +5707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A129">
         <v>19</v>
       </c>
@@ -5728,7 +5736,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A130">
         <v>15</v>
       </c>
@@ -5757,7 +5765,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A131">
         <v>31</v>
       </c>
@@ -5786,7 +5794,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A132">
         <v>26</v>
       </c>
@@ -5815,7 +5823,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A133">
         <v>32</v>
       </c>
@@ -5844,7 +5852,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A134">
         <v>25</v>
       </c>
@@ -5873,7 +5881,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A135">
         <v>16</v>
       </c>
@@ -5902,7 +5910,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A136">
         <v>16</v>
       </c>
@@ -5931,7 +5939,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A137">
         <v>18</v>
       </c>
@@ -5960,7 +5968,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A138">
         <v>16</v>
       </c>
@@ -5989,7 +5997,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A139">
         <v>13</v>
       </c>
@@ -6018,7 +6026,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A140">
         <v>14</v>
       </c>
@@ -6047,7 +6055,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A141">
         <v>14</v>
       </c>
@@ -6076,7 +6084,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A142">
         <v>14</v>
       </c>
@@ -6105,7 +6113,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A143">
         <v>29</v>
       </c>
@@ -6134,7 +6142,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A144">
         <v>26</v>
       </c>
@@ -6163,7 +6171,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A145">
         <v>26</v>
       </c>
@@ -6192,7 +6200,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A146">
         <v>31</v>
       </c>
@@ -6221,7 +6229,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A147">
         <v>32</v>
       </c>
@@ -6250,7 +6258,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A148">
         <v>28</v>
       </c>
@@ -6279,7 +6287,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A149">
         <v>24</v>
       </c>
@@ -6308,7 +6316,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A150">
         <v>26</v>
       </c>
@@ -6337,7 +6345,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A151">
         <v>24</v>
       </c>
@@ -6366,7 +6374,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A152">
         <v>26</v>
       </c>
@@ -6395,7 +6403,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A153">
         <v>31</v>
       </c>
@@ -6424,7 +6432,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A154">
         <v>19</v>
       </c>
@@ -6453,7 +6461,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A155">
         <v>18</v>
       </c>
@@ -6482,7 +6490,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A156">
         <v>15</v>
       </c>
@@ -6511,7 +6519,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A157">
         <v>15</v>
       </c>
@@ -6540,7 +6548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A158">
         <v>16</v>
       </c>
@@ -6569,7 +6577,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A159">
         <v>15</v>
       </c>
@@ -6598,7 +6606,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A160">
         <v>16</v>
       </c>
@@ -6627,7 +6635,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A161">
         <v>14</v>
       </c>
@@ -6656,7 +6664,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A162">
         <v>17</v>
       </c>
@@ -6685,7 +6693,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A163">
         <v>16</v>
       </c>
@@ -6714,7 +6722,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A164">
         <v>15</v>
       </c>
@@ -6743,7 +6751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A165">
         <v>18</v>
       </c>
@@ -6772,7 +6780,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A166">
         <v>21</v>
       </c>
@@ -6801,7 +6809,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A167">
         <v>20</v>
       </c>
@@ -6830,7 +6838,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A168">
         <v>13</v>
       </c>
@@ -6859,7 +6867,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A169">
         <v>29</v>
       </c>
@@ -6888,7 +6896,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A170">
         <v>23</v>
       </c>
@@ -6917,7 +6925,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A171">
         <v>20</v>
       </c>
@@ -6946,7 +6954,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A172">
         <v>23</v>
       </c>
@@ -6975,7 +6983,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A173">
         <v>24</v>
       </c>
@@ -7004,7 +7012,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A174">
         <v>25</v>
       </c>
@@ -7033,7 +7041,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A175">
         <v>24</v>
       </c>
@@ -7062,7 +7070,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A176">
         <v>18</v>
       </c>
@@ -7091,7 +7099,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A177">
         <v>29</v>
       </c>
@@ -7120,7 +7128,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A178">
         <v>19</v>
       </c>
@@ -7149,7 +7157,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A179">
         <v>23</v>
       </c>
@@ -7178,7 +7186,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A180">
         <v>23</v>
       </c>
@@ -7207,7 +7215,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A181">
         <v>22</v>
       </c>
@@ -7236,7 +7244,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A182">
         <v>25</v>
       </c>
@@ -7265,7 +7273,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A183">
         <v>33</v>
       </c>
@@ -7294,7 +7302,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A184">
         <v>28</v>
       </c>
@@ -7323,7 +7331,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A185">
         <v>25</v>
       </c>
@@ -7352,7 +7360,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A186">
         <v>25</v>
       </c>
@@ -7381,7 +7389,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A187">
         <v>26</v>
       </c>
@@ -7410,7 +7418,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A188">
         <v>27</v>
       </c>
@@ -7439,7 +7447,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A189">
         <v>17.5</v>
       </c>
@@ -7468,7 +7476,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A190">
         <v>16</v>
       </c>
@@ -7497,7 +7505,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A191">
         <v>15.5</v>
       </c>
@@ -7526,7 +7534,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A192">
         <v>14.5</v>
       </c>
@@ -7555,7 +7563,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A193">
         <v>22</v>
       </c>
@@ -7584,7 +7592,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A194">
         <v>22</v>
       </c>
@@ -7613,7 +7621,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A195">
         <v>24</v>
       </c>
@@ -7642,7 +7650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A196">
         <v>22.5</v>
       </c>
@@ -7671,7 +7679,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A197">
         <v>29</v>
       </c>
@@ -7700,7 +7708,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A198">
         <v>24.5</v>
       </c>
@@ -7729,7 +7737,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A199">
         <v>29</v>
       </c>
@@ -7758,7 +7766,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A200">
         <v>33</v>
       </c>
@@ -7787,7 +7795,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A201">
         <v>20</v>
       </c>
@@ -7816,7 +7824,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A202">
         <v>18</v>
       </c>
@@ -7845,7 +7853,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A203">
         <v>18.5</v>
       </c>
@@ -7874,7 +7882,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A204">
         <v>17.5</v>
       </c>
@@ -7903,7 +7911,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A205">
         <v>29.5</v>
       </c>
@@ -7932,7 +7940,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A206">
         <v>32</v>
       </c>
@@ -7961,7 +7969,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A207">
         <v>28</v>
       </c>
@@ -7990,7 +7998,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A208">
         <v>26.5</v>
       </c>
@@ -8019,7 +8027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A209">
         <v>20</v>
       </c>
@@ -8048,7 +8056,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A210">
         <v>13</v>
       </c>
@@ -8077,7 +8085,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A211">
         <v>19</v>
       </c>
@@ -8106,7 +8114,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A212">
         <v>19</v>
       </c>
@@ -8135,7 +8143,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A213">
         <v>16.5</v>
       </c>
@@ -8164,7 +8172,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A214">
         <v>16.5</v>
       </c>
@@ -8193,7 +8201,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A215">
         <v>13</v>
       </c>
@@ -8222,7 +8230,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A216">
         <v>13</v>
       </c>
@@ -8251,7 +8259,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A217">
         <v>13</v>
       </c>
@@ -8280,7 +8288,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A218">
         <v>31.5</v>
       </c>
@@ -8309,7 +8317,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A219">
         <v>30</v>
       </c>
@@ -8338,7 +8346,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A220">
         <v>36</v>
       </c>
@@ -8367,7 +8375,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A221">
         <v>25.5</v>
       </c>
@@ -8396,7 +8404,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A222">
         <v>33.5</v>
       </c>
@@ -8425,7 +8433,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A223">
         <v>17.5</v>
       </c>
@@ -8454,7 +8462,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A224">
         <v>17</v>
       </c>
@@ -8483,7 +8491,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A225">
         <v>15.5</v>
       </c>
@@ -8512,7 +8520,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A226">
         <v>15</v>
       </c>
@@ -8541,7 +8549,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A227">
         <v>17.5</v>
       </c>
@@ -8570,7 +8578,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A228">
         <v>20.5</v>
       </c>
@@ -8599,7 +8607,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A229">
         <v>19</v>
       </c>
@@ -8628,7 +8636,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A230">
         <v>18.5</v>
       </c>
@@ -8657,7 +8665,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A231">
         <v>16</v>
       </c>
@@ -8686,7 +8694,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A232">
         <v>15.5</v>
       </c>
@@ -8715,7 +8723,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A233">
         <v>15.5</v>
       </c>
@@ -8744,7 +8752,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A234">
         <v>16</v>
       </c>
@@ -8773,7 +8781,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A235">
         <v>29</v>
       </c>
@@ -8802,7 +8810,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A236">
         <v>24.5</v>
       </c>
@@ -8831,7 +8839,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A237">
         <v>26</v>
       </c>
@@ -8860,7 +8868,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A238">
         <v>25.5</v>
       </c>
@@ -8889,7 +8897,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A239">
         <v>30.5</v>
       </c>
@@ -8918,7 +8926,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A240">
         <v>33.5</v>
       </c>
@@ -8947,7 +8955,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A241">
         <v>30</v>
       </c>
@@ -8976,7 +8984,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A242">
         <v>30.5</v>
       </c>
@@ -9005,7 +9013,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A243">
         <v>22</v>
       </c>
@@ -9034,7 +9042,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A244">
         <v>21.5</v>
       </c>
@@ -9063,7 +9071,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A245">
         <v>21.5</v>
       </c>
@@ -9092,7 +9100,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A246">
         <v>43.1</v>
       </c>
@@ -9121,7 +9129,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A247">
         <v>36.1</v>
       </c>
@@ -9150,7 +9158,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A248">
         <v>32.799999999999997</v>
       </c>
@@ -9179,7 +9187,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A249">
         <v>39.4</v>
       </c>
@@ -9208,7 +9216,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A250">
         <v>36.1</v>
       </c>
@@ -9237,7 +9245,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A251">
         <v>19.899999999999999</v>
       </c>
@@ -9266,7 +9274,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A252">
         <v>19.399999999999999</v>
       </c>
@@ -9295,7 +9303,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A253">
         <v>20.2</v>
       </c>
@@ -9324,7 +9332,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A254">
         <v>19.2</v>
       </c>
@@ -9353,7 +9361,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A255">
         <v>20.5</v>
       </c>
@@ -9382,7 +9390,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A256">
         <v>20.2</v>
       </c>
@@ -9411,7 +9419,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A257">
         <v>25.1</v>
       </c>
@@ -9440,7 +9448,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A258">
         <v>20.5</v>
       </c>
@@ -9469,7 +9477,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A259">
         <v>19.399999999999999</v>
       </c>
@@ -9498,7 +9506,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A260">
         <v>20.6</v>
       </c>
@@ -9527,7 +9535,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A261">
         <v>20.8</v>
       </c>
@@ -9556,7 +9564,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A262">
         <v>18.600000000000001</v>
       </c>
@@ -9585,7 +9593,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A263">
         <v>18.100000000000001</v>
       </c>
@@ -9614,7 +9622,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A264">
         <v>19.2</v>
       </c>
@@ -9643,7 +9651,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A265">
         <v>17.7</v>
       </c>
@@ -9672,7 +9680,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A266">
         <v>18.100000000000001</v>
       </c>
@@ -9701,7 +9709,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A267">
         <v>17.5</v>
       </c>
@@ -9730,7 +9738,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A268">
         <v>30</v>
       </c>
@@ -9759,7 +9767,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A269">
         <v>27.5</v>
       </c>
@@ -9788,7 +9796,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A270">
         <v>27.2</v>
       </c>
@@ -9817,7 +9825,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A271">
         <v>30.9</v>
       </c>
@@ -9846,7 +9854,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A272">
         <v>21.1</v>
       </c>
@@ -9875,7 +9883,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A273">
         <v>23.2</v>
       </c>
@@ -9904,7 +9912,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A274">
         <v>23.8</v>
       </c>
@@ -9933,7 +9941,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A275">
         <v>23.9</v>
       </c>
@@ -9962,7 +9970,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A276">
         <v>20.3</v>
       </c>
@@ -9991,7 +9999,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A277">
         <v>17</v>
       </c>
@@ -10020,7 +10028,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A278">
         <v>21.6</v>
       </c>
@@ -10049,7 +10057,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A279">
         <v>16.2</v>
       </c>
@@ -10078,7 +10086,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A280">
         <v>31.5</v>
       </c>
@@ -10107,7 +10115,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A281">
         <v>29.5</v>
       </c>
@@ -10136,7 +10144,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A282">
         <v>21.5</v>
       </c>
@@ -10165,7 +10173,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A283">
         <v>19.8</v>
       </c>
@@ -10194,7 +10202,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A284">
         <v>22.3</v>
       </c>
@@ -10223,7 +10231,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A285">
         <v>20.2</v>
       </c>
@@ -10252,7 +10260,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A286">
         <v>20.6</v>
       </c>
@@ -10281,7 +10289,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10310,7 +10318,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A288">
         <v>17.600000000000001</v>
       </c>
@@ -10339,7 +10347,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A289">
         <v>16.5</v>
       </c>
@@ -10368,7 +10376,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A290">
         <v>18.2</v>
       </c>
@@ -10397,7 +10405,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A291">
         <v>16.899999999999999</v>
       </c>
@@ -10426,7 +10434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A292">
         <v>15.5</v>
       </c>
@@ -10455,7 +10463,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A293">
         <v>19.2</v>
       </c>
@@ -10484,7 +10492,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A294">
         <v>18.5</v>
       </c>
@@ -10513,7 +10521,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A295">
         <v>31.9</v>
       </c>
@@ -10542,7 +10550,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A296">
         <v>34.1</v>
       </c>
@@ -10571,7 +10579,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A297">
         <v>35.700000000000003</v>
       </c>
@@ -10600,7 +10608,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A298">
         <v>27.4</v>
       </c>
@@ -10629,7 +10637,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A299">
         <v>25.4</v>
       </c>
@@ -10658,7 +10666,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A300">
         <v>23</v>
       </c>
@@ -10687,7 +10695,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A301">
         <v>27.2</v>
       </c>
@@ -10716,7 +10724,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A302">
         <v>23.9</v>
       </c>
@@ -10745,7 +10753,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A303">
         <v>34.200000000000003</v>
       </c>
@@ -10774,7 +10782,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A304">
         <v>34.5</v>
       </c>
@@ -10803,7 +10811,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A305">
         <v>31.8</v>
       </c>
@@ -10832,7 +10840,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A306">
         <v>37.299999999999997</v>
       </c>
@@ -10861,7 +10869,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A307">
         <v>28.4</v>
       </c>
@@ -10890,7 +10898,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A308">
         <v>28.8</v>
       </c>
@@ -10919,7 +10927,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A309">
         <v>26.8</v>
       </c>
@@ -10948,7 +10956,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A310">
         <v>33.5</v>
       </c>
@@ -10977,7 +10985,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A311">
         <v>41.5</v>
       </c>
@@ -11006,7 +11014,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A312">
         <v>38.1</v>
       </c>
@@ -11035,7 +11043,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A313">
         <v>32.1</v>
       </c>
@@ -11064,7 +11072,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A314">
         <v>37.200000000000003</v>
       </c>
@@ -11093,7 +11101,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A315">
         <v>28</v>
       </c>
@@ -11122,7 +11130,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A316">
         <v>26.4</v>
       </c>
@@ -11151,7 +11159,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A317">
         <v>24.3</v>
       </c>
@@ -11180,7 +11188,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A318">
         <v>19.100000000000001</v>
       </c>
@@ -11209,7 +11217,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A319">
         <v>34.299999999999997</v>
       </c>
@@ -11238,7 +11246,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A320">
         <v>29.8</v>
       </c>
@@ -11267,7 +11275,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A321">
         <v>31.3</v>
       </c>
@@ -11296,7 +11304,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A322">
         <v>37</v>
       </c>
@@ -11325,7 +11333,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A323">
         <v>32.200000000000003</v>
       </c>
@@ -11354,7 +11362,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A324">
         <v>46.6</v>
       </c>
@@ -11383,7 +11391,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A325">
         <v>27.9</v>
       </c>
@@ -11412,7 +11420,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A326">
         <v>40.799999999999997</v>
       </c>
@@ -11441,7 +11449,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A327">
         <v>44.3</v>
       </c>
@@ -11470,7 +11478,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A328">
         <v>43.4</v>
       </c>
@@ -11499,7 +11507,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A329">
         <v>36.4</v>
       </c>
@@ -11528,7 +11536,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A330">
         <v>30</v>
       </c>
@@ -11557,7 +11565,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A331">
         <v>44.6</v>
       </c>
@@ -11586,7 +11594,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A332">
         <v>40.9</v>
       </c>
@@ -11612,7 +11620,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A333">
         <v>33.799999999999997</v>
       </c>
@@ -11641,7 +11649,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A334">
         <v>29.8</v>
       </c>
@@ -11670,7 +11678,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A335">
         <v>32.700000000000003</v>
       </c>
@@ -11699,7 +11707,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A336">
         <v>23.7</v>
       </c>
@@ -11728,7 +11736,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A337">
         <v>35</v>
       </c>
@@ -11757,7 +11765,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A338">
         <v>23.6</v>
       </c>
@@ -11783,7 +11791,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A339">
         <v>32.4</v>
       </c>
@@ -11812,7 +11820,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A340">
         <v>27.2</v>
       </c>
@@ -11841,7 +11849,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A341">
         <v>26.6</v>
       </c>
@@ -11870,7 +11878,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A342">
         <v>25.8</v>
       </c>
@@ -11899,7 +11907,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A343">
         <v>23.5</v>
       </c>
@@ -11928,7 +11936,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A344">
         <v>30</v>
       </c>
@@ -11957,7 +11965,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A345">
         <v>39.1</v>
       </c>
@@ -11986,7 +11994,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A346">
         <v>39</v>
       </c>
@@ -12015,7 +12023,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A347">
         <v>35.1</v>
       </c>
@@ -12044,7 +12052,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A348">
         <v>32.299999999999997</v>
       </c>
@@ -12073,7 +12081,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A349">
         <v>37</v>
       </c>
@@ -12102,7 +12110,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A350">
         <v>37.700000000000003</v>
       </c>
@@ -12131,7 +12139,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A351">
         <v>34.1</v>
       </c>
@@ -12160,7 +12168,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A352">
         <v>34.700000000000003</v>
       </c>
@@ -12189,7 +12197,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A353">
         <v>34.4</v>
       </c>
@@ -12218,7 +12226,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A354">
         <v>29.9</v>
       </c>
@@ -12247,7 +12255,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A355">
         <v>33</v>
       </c>
@@ -12276,7 +12284,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A356">
         <v>34.5</v>
       </c>
@@ -12302,7 +12310,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A357">
         <v>33.700000000000003</v>
       </c>
@@ -12331,7 +12339,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A358">
         <v>32.4</v>
       </c>
@@ -12360,7 +12368,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A359">
         <v>32.9</v>
       </c>
@@ -12389,7 +12397,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A360">
         <v>31.6</v>
       </c>
@@ -12418,7 +12426,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A361">
         <v>28.1</v>
       </c>
@@ -12447,7 +12455,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A362">
         <v>30.7</v>
       </c>
@@ -12476,7 +12484,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A363">
         <v>25.4</v>
       </c>
@@ -12505,7 +12513,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A364">
         <v>24.2</v>
       </c>
@@ -12534,7 +12542,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A365">
         <v>22.4</v>
       </c>
@@ -12563,7 +12571,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A366">
         <v>26.6</v>
       </c>
@@ -12592,7 +12600,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A367">
         <v>20.2</v>
       </c>
@@ -12621,7 +12629,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A368">
         <v>17.600000000000001</v>
       </c>
@@ -12650,7 +12658,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A369">
         <v>28</v>
       </c>
@@ -12679,7 +12687,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A370">
         <v>27</v>
       </c>
@@ -12708,7 +12716,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A371">
         <v>34</v>
       </c>
@@ -12737,7 +12745,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A372">
         <v>31</v>
       </c>
@@ -12766,7 +12774,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A373">
         <v>29</v>
       </c>
@@ -12795,7 +12803,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A374">
         <v>27</v>
       </c>
@@ -12824,7 +12832,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A375">
         <v>24</v>
       </c>
@@ -12853,7 +12861,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A376">
         <v>23</v>
       </c>
@@ -12879,7 +12887,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A377">
         <v>36</v>
       </c>
@@ -12908,7 +12916,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A378">
         <v>37</v>
       </c>
@@ -12937,7 +12945,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A379">
         <v>31</v>
       </c>
@@ -12966,7 +12974,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A380">
         <v>38</v>
       </c>
@@ -12995,7 +13003,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A381">
         <v>36</v>
       </c>
@@ -13024,7 +13032,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A382">
         <v>36</v>
       </c>
@@ -13053,7 +13061,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A383">
         <v>36</v>
       </c>
@@ -13082,7 +13090,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A384">
         <v>34</v>
       </c>
@@ -13111,7 +13119,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A385">
         <v>38</v>
       </c>
@@ -13140,7 +13148,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A386">
         <v>32</v>
       </c>
@@ -13169,7 +13177,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A387">
         <v>38</v>
       </c>
@@ -13198,7 +13206,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A388">
         <v>25</v>
       </c>
@@ -13227,7 +13235,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A389">
         <v>38</v>
       </c>
@@ -13256,7 +13264,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A390">
         <v>26</v>
       </c>
@@ -13285,7 +13293,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A391">
         <v>22</v>
       </c>
@@ -13314,7 +13322,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A392">
         <v>32</v>
       </c>
@@ -13343,7 +13351,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A393">
         <v>36</v>
       </c>
@@ -13372,7 +13380,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A394">
         <v>27</v>
       </c>
@@ -13401,7 +13409,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A395">
         <v>27</v>
       </c>
@@ -13430,7 +13438,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A396">
         <v>44</v>
       </c>
@@ -13459,7 +13467,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A397">
         <v>32</v>
       </c>
@@ -13488,7 +13496,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A398">
         <v>28</v>
       </c>
@@ -13517,7 +13525,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A399">
         <v>31</v>
       </c>
@@ -13558,19 +13566,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FBD565-4521-4E30-A67D-FF1FDA2E9337}">
   <dimension ref="A1:I95"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="13.19921875" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.19921875" customWidth="1"/>
-    <col min="6" max="6" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.17578125" customWidth="1"/>
+    <col min="2" max="2" width="30.3515625" customWidth="1"/>
+    <col min="3" max="3" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.17578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.17578125" customWidth="1"/>
+    <col min="6" max="6" width="10.46875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1171875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.05859375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A1" t="str" cm="1">
         <f t="array" ref="A1:F10">_xlfn._xlws.PY(1,0)</f>
         <v/>
@@ -13591,7 +13599,7 @@
         <v>unique</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A2" t="str">
         <v>mpg</v>
       </c>
@@ -13611,7 +13619,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" t="str">
         <v>cylinders</v>
       </c>
@@ -13631,7 +13639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A4" t="str">
         <v>displacement</v>
       </c>
@@ -13651,7 +13659,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" t="str">
         <v>horsepower</v>
       </c>
@@ -13671,7 +13679,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A6" t="str">
         <v>weight</v>
       </c>
@@ -13691,7 +13699,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A7" t="str">
         <v>acceleration</v>
       </c>
@@ -13711,7 +13719,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A8" t="str">
         <v>model_year</v>
       </c>
@@ -13731,7 +13739,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A9" t="str">
         <v>origin</v>
       </c>
@@ -13751,7 +13759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A10" t="str">
         <v>name</v>
       </c>
@@ -13771,7 +13779,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="str" cm="1">
         <f t="array" ref="A14:I19">_xlfn._xlws.PY(2,0)</f>
         <v>mpg</v>
@@ -13801,7 +13809,7 @@
         <v>name</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
         <v>18</v>
       </c>
@@ -13830,7 +13838,7 @@
         <v>chevrolet chevelle malibu</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -13859,7 +13867,7 @@
         <v>buick skylark 320</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
         <v>18</v>
       </c>
@@ -13888,7 +13896,7 @@
         <v>plymouth satellite</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -13917,7 +13925,7 @@
         <v>amc rebel sst</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -13946,19 +13954,19 @@
         <v>ford torino</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" t="str" cm="1">
         <f t="array" ref="A21">_xlfn._xlws.PY(3,0)</f>
         <v>Before: 398 rows, After: 392 rows, Removed: 6</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23" t="str" cm="1">
         <f t="array" ref="A23">_xlfn._xlws.PY(4,0)</f>
         <v>Median horsepower: 93.5, Missing after fill: 0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A25" t="str" cm="1">
         <f t="array" ref="A25:C30">_xlfn._xlws.PY(5,0)</f>
         <v>name</v>
@@ -13970,7 +13978,7 @@
         <v>era</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A26" t="str">
         <v>chevrolet chevelle malibu</v>
       </c>
@@ -13981,7 +13989,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A27" t="str">
         <v>buick skylark 320</v>
       </c>
@@ -13992,7 +14000,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A28" t="str">
         <v>plymouth satellite</v>
       </c>
@@ -14003,7 +14011,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A29" t="str">
         <v>amc rebel sst</v>
       </c>
@@ -14014,7 +14022,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A30" t="str">
         <v>ford torino</v>
       </c>
@@ -14025,7 +14033,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A33" t="str" cm="1">
         <f t="array" ref="A33:B36">_xlfn._xlws.PY(6,0)</f>
         <v>origin</v>
@@ -14034,7 +14042,7 @@
         <v>power_to_weight</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A34" t="str">
         <v>europe</v>
       </c>
@@ -14042,7 +14050,7 @@
         <v>33.69</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A35" t="str">
         <v>japan</v>
       </c>
@@ -14050,7 +14058,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A36" t="str">
         <v>usa</v>
       </c>
@@ -14058,7 +14066,7 @@
         <v>34.97</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A39" t="str" cm="1">
         <f t="array" ref="A39:F43">_xlfn._xlws.PY(7,0)</f>
         <v>cylinders</v>
@@ -14079,7 +14087,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A40" t="str">
         <v>origin</v>
       </c>
@@ -14099,7 +14107,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A41" t="str">
         <v>europe</v>
       </c>
@@ -14119,7 +14127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A42" t="str">
         <v>japan</v>
       </c>
@@ -14139,7 +14147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A43" t="str">
         <v>usa</v>
       </c>
@@ -14159,7 +14167,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A46" t="str" cm="1">
         <f t="array" ref="A46:F50">_xlfn._xlws.PY(8,0)</f>
         <v>cylinders</v>
@@ -14180,7 +14188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A47" t="str">
         <v>origin</v>
       </c>
@@ -14200,7 +14208,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A48" t="str">
         <v>europe</v>
       </c>
@@ -14220,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A49" t="str">
         <v>japan</v>
       </c>
@@ -14240,7 +14248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A50" t="str">
         <v>usa</v>
       </c>
@@ -14260,19 +14268,19 @@
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A54" t="e" cm="1" vm="2">
         <f t="array" ref="A54">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.5">
       <c r="A74" t="e" cm="1" vm="3">
         <f t="array" ref="A74">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A89" t="str" cm="1">
         <f t="array" ref="A89:G92">_xlfn._xlws.PY(11,0)</f>
         <v/>
@@ -14296,7 +14304,7 @@
         <v>model_year</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A90">
         <v>344</v>
       </c>
@@ -14319,7 +14327,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A91">
         <v>378</v>
       </c>
@@ -14342,7 +14350,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A92">
         <v>387</v>
       </c>
@@ -14365,7 +14373,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A95" t="e" cm="1" vm="4">
         <f t="array" ref="A95">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>
